--- a/controls_bs.xlsx
+++ b/controls_bs.xlsx
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.2609239131116862</v>
+        <v>0.23794517107807</v>
       </c>
       <c r="F2">
-        <v>0.08210885541902428</v>
+        <v>0.08440892429708842</v>
       </c>
       <c r="G2">
-        <v>3.177780420639395</v>
+        <v>2.81895751023423</v>
       </c>
       <c r="H2">
-        <v>0.001484070986543748</v>
+        <v>0.004817989537098957</v>
       </c>
       <c r="I2">
-        <v>0.09999351367859222</v>
+        <v>0.07250671948200879</v>
       </c>
       <c r="J2">
-        <v>0.4218543125447802</v>
+        <v>0.4033836226741311</v>
       </c>
     </row>
     <row r="3">
@@ -458,22 +458,22 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.6587972572926559</v>
+        <v>0.5164827950732737</v>
       </c>
       <c r="F3">
-        <v>0.2320514114333367</v>
+        <v>0.225957815482257</v>
       </c>
       <c r="G3">
-        <v>2.839014221992414</v>
+        <v>2.285748753460709</v>
       </c>
       <c r="H3">
-        <v>0.004525313993207375</v>
+        <v>0.02226896127918899</v>
       </c>
       <c r="I3">
-        <v>0.2039848483216301</v>
+        <v>0.07361361470270311</v>
       </c>
       <c r="J3">
-        <v>1.113609666263682</v>
+        <v>0.9593519754438442</v>
       </c>
     </row>
     <row r="4">
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="E4">
-        <v>-0.04695213790336836</v>
+        <v>-0.2738393710814888</v>
       </c>
       <c r="F4">
-        <v>0.09631155440378124</v>
+        <v>0.09626954456259493</v>
       </c>
       <c r="G4">
-        <v>-0.4875026490230231</v>
+        <v>-2.844506768217202</v>
       </c>
       <c r="H4">
-        <v>0.6259021660309343</v>
+        <v>0.004448024084046628</v>
       </c>
       <c r="I4">
-        <v>-0.2357193158298496</v>
+        <v>-0.4625242112322486</v>
       </c>
       <c r="J4">
-        <v>0.1418150400231129</v>
+        <v>-0.085154530930729</v>
       </c>
     </row>
     <row r="5">
@@ -528,22 +528,22 @@
         </is>
       </c>
       <c r="E5">
-        <v>0.1102668997702695</v>
+        <v>-0.1384241366249296</v>
       </c>
       <c r="F5">
-        <v>0.131281061835783</v>
+        <v>0.1267827737943085</v>
       </c>
       <c r="G5">
-        <v>0.8399299809762381</v>
+        <v>-1.091821329366937</v>
       </c>
       <c r="H5">
-        <v>0.4009476464753177</v>
+        <v>0.2749116419823678</v>
       </c>
       <c r="I5">
-        <v>-0.1470392532800409</v>
+        <v>-0.3869138071218627</v>
       </c>
       <c r="J5">
-        <v>0.3675730528205799</v>
+        <v>0.1100655338720037</v>
       </c>
     </row>
     <row r="6">
@@ -563,22 +563,22 @@
         </is>
       </c>
       <c r="E6">
-        <v>0.4830977129553419</v>
+        <v>0.4407863193415568</v>
       </c>
       <c r="F6">
-        <v>0.2164899534973703</v>
+        <v>0.221035437313047</v>
       </c>
       <c r="G6">
-        <v>2.231501763250229</v>
+        <v>1.994188464527894</v>
       </c>
       <c r="H6">
-        <v>0.0256479108503848</v>
+        <v>0.04613146231380465</v>
       </c>
       <c r="I6">
-        <v>0.05878520108574514</v>
+        <v>0.007564822900923918</v>
       </c>
       <c r="J6">
-        <v>0.9074102248249387</v>
+        <v>0.8740078157821898</v>
       </c>
     </row>
     <row r="7">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="E7">
-        <v>0.2627822424860271</v>
+        <v>0.248410126460625</v>
       </c>
       <c r="F7">
-        <v>0.1449693103235144</v>
+        <v>0.1448262125184845</v>
       </c>
       <c r="G7">
-        <v>1.812674985482104</v>
+        <v>1.715229046875198</v>
       </c>
       <c r="H7">
-        <v>0.06988196480660638</v>
+        <v>0.08630324134098739</v>
       </c>
       <c r="I7">
-        <v>-0.02135238461167177</v>
+        <v>-0.03544403409294836</v>
       </c>
       <c r="J7">
-        <v>0.5469168695837259</v>
+        <v>0.5322642870141984</v>
       </c>
     </row>
     <row r="8">
@@ -633,22 +633,22 @@
         </is>
       </c>
       <c r="E8">
-        <v>-0.2296046339293768</v>
+        <v>-0.1430028620669192</v>
       </c>
       <c r="F8">
-        <v>0.1678457491191464</v>
+        <v>0.1681059303189169</v>
       </c>
       <c r="G8">
-        <v>-1.367950246785162</v>
+        <v>-0.8506711321583109</v>
       </c>
       <c r="H8">
-        <v>0.1713276501527679</v>
+        <v>0.3949520634880102</v>
       </c>
       <c r="I8">
-        <v>-0.5585762571610492</v>
+        <v>-0.4724844310795961</v>
       </c>
       <c r="J8">
-        <v>0.09936698930229562</v>
+        <v>0.1864787069457578</v>
       </c>
     </row>
     <row r="9">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="E9">
-        <v>0.4501718666312338</v>
+        <v>0.3416553087791496</v>
       </c>
       <c r="F9">
-        <v>0.04221666188544133</v>
+        <v>0.04156749676335684</v>
       </c>
       <c r="G9">
-        <v>10.66336954477394</v>
+        <v>8.219289959272468</v>
       </c>
       <c r="H9">
-        <v>1.5102459812406E-26</v>
+        <v>2.047115501540899E-16</v>
       </c>
       <c r="I9">
-        <v>0.367428729788264</v>
+        <v>0.260184512195485</v>
       </c>
       <c r="J9">
-        <v>0.5329150034742036</v>
+        <v>0.4231261053628143</v>
       </c>
     </row>
     <row r="10">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.294663924057547</v>
+        <v>0.2923067510763435</v>
       </c>
       <c r="F10">
-        <v>0.08166641438712362</v>
+        <v>0.09523496013171492</v>
       </c>
       <c r="G10">
-        <v>3.608140828379589</v>
+        <v>3.069321924134456</v>
       </c>
       <c r="H10">
-        <v>0.000308399084455757</v>
+        <v>0.002145452670729041</v>
       </c>
       <c r="I10">
-        <v>0.134600693112261</v>
+        <v>0.1056496591490743</v>
       </c>
       <c r="J10">
-        <v>0.454727155002833</v>
+        <v>0.4789638430036126</v>
       </c>
     </row>
     <row r="11">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="E11">
-        <v>0.4936911271055117</v>
+        <v>0.4991744451726671</v>
       </c>
       <c r="F11">
-        <v>0.2541732388385929</v>
+        <v>0.289449566569678</v>
       </c>
       <c r="G11">
-        <v>1.942341095236306</v>
+        <v>1.72456449352638</v>
       </c>
       <c r="H11">
-        <v>0.05209582116010652</v>
+        <v>0.08460598686699924</v>
       </c>
       <c r="I11">
-        <v>-0.004479266852027486</v>
+        <v>-0.06813628064463045</v>
       </c>
       <c r="J11">
-        <v>0.9918615210630509</v>
+        <v>1.066485170989965</v>
       </c>
     </row>
     <row r="12">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="E12">
-        <v>-0.1235644176914057</v>
+        <v>-0.3775623939081602</v>
       </c>
       <c r="F12">
-        <v>0.1156154905871214</v>
+        <v>0.1203806418775955</v>
       </c>
       <c r="G12">
-        <v>-1.06875313216177</v>
+        <v>-3.136404558235121</v>
       </c>
       <c r="H12">
-        <v>0.2851809231115929</v>
+        <v>0.001710330949962736</v>
       </c>
       <c r="I12">
-        <v>-0.3501666152970933</v>
+        <v>-0.6135041164240616</v>
       </c>
       <c r="J12">
-        <v>0.1030377799142819</v>
+        <v>-0.1416206713922589</v>
       </c>
     </row>
     <row r="13">
@@ -808,22 +808,22 @@
         </is>
       </c>
       <c r="E13">
-        <v>-0.1430412417872818</v>
+        <v>-0.3396921864825909</v>
       </c>
       <c r="F13">
-        <v>0.1574464568210432</v>
+        <v>0.1524430942885356</v>
       </c>
       <c r="G13">
-        <v>-0.9085072136609927</v>
+        <v>-2.228321250417817</v>
       </c>
       <c r="H13">
-        <v>0.3636103042680376</v>
+        <v>0.02585910025612928</v>
       </c>
       <c r="I13">
-        <v>-0.4516306266499671</v>
+        <v>-0.6384751609799642</v>
       </c>
       <c r="J13">
-        <v>0.1655481430754036</v>
+        <v>-0.04090921198521758</v>
       </c>
     </row>
     <row r="14">
@@ -843,22 +843,22 @@
         </is>
       </c>
       <c r="E14">
-        <v>0.6206518139759015</v>
+        <v>0.5217089844717735</v>
       </c>
       <c r="F14">
-        <v>0.2425187615687055</v>
+        <v>0.2668521333532986</v>
       </c>
       <c r="G14">
-        <v>2.559190925936141</v>
+        <v>1.955048955074522</v>
       </c>
       <c r="H14">
-        <v>0.01049161026842176</v>
+        <v>0.05057729230672995</v>
       </c>
       <c r="I14">
-        <v>0.1453237757259823</v>
+        <v>-0.001311586098371342</v>
       </c>
       <c r="J14">
-        <v>1.095979852225821</v>
+        <v>1.044729555041918</v>
       </c>
     </row>
     <row r="15">
@@ -878,22 +878,22 @@
         </is>
       </c>
       <c r="E15">
-        <v>0.3954594693987208</v>
+        <v>0.4390881287207283</v>
       </c>
       <c r="F15">
-        <v>0.1625884581942248</v>
+        <v>0.1935490160640914</v>
       </c>
       <c r="G15">
-        <v>2.432272707367169</v>
+        <v>2.268614626154078</v>
       </c>
       <c r="H15">
-        <v>0.01500440548800116</v>
+        <v>0.0232917713849704</v>
       </c>
       <c r="I15">
-        <v>0.07679194703614406</v>
+        <v>0.05973902799194486</v>
       </c>
       <c r="J15">
-        <v>0.7141269917612976</v>
+        <v>0.8184372294495118</v>
       </c>
     </row>
     <row r="16">
@@ -913,22 +913,22 @@
         </is>
       </c>
       <c r="E16">
-        <v>-0.03785311764151554</v>
+        <v>0.2557716233019834</v>
       </c>
       <c r="F16">
-        <v>0.18259162175809</v>
+        <v>0.2299361111185921</v>
       </c>
       <c r="G16">
-        <v>-0.2073102658109141</v>
+        <v>1.112359524816293</v>
       </c>
       <c r="H16">
-        <v>0.835767557341588</v>
+        <v>0.2659835999874571</v>
       </c>
       <c r="I16">
-        <v>-0.3957261201661321</v>
+        <v>-0.1948948732356568</v>
       </c>
       <c r="J16">
-        <v>0.320019884883101</v>
+        <v>0.7064381198396237</v>
       </c>
     </row>
     <row r="17">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.4068172888144626</v>
+        <v>0.4269207869480741</v>
       </c>
       <c r="F17">
-        <v>0.05838996274126594</v>
+        <v>0.0494495196055302</v>
       </c>
       <c r="G17">
-        <v>6.967246932784093</v>
+        <v>8.633466823413372</v>
       </c>
       <c r="H17">
-        <v>3.232031057842726E-12</v>
+        <v>5.951992491058056E-18</v>
       </c>
       <c r="I17">
-        <v>0.2923750647829457</v>
+        <v>0.3300015094684276</v>
       </c>
       <c r="J17">
-        <v>0.5212595128459795</v>
+        <v>0.5238400644277206</v>
       </c>
     </row>
     <row r="18">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E18">
-        <v>0.3898129371342249</v>
+        <v>0.3763290348285415</v>
       </c>
       <c r="F18">
-        <v>0.09012655106822186</v>
+        <v>0.1025833139846096</v>
       </c>
       <c r="G18">
-        <v>4.325173131712913</v>
+        <v>3.66852093396984</v>
       </c>
       <c r="H18">
-        <v>1.524121113184554E-05</v>
+        <v>0.0002439577217477563</v>
       </c>
       <c r="I18">
-        <v>0.2131681429897002</v>
+        <v>0.1752694340039426</v>
       </c>
       <c r="J18">
-        <v>0.5664577312787497</v>
+        <v>0.5773886356531405</v>
       </c>
     </row>
     <row r="19">
@@ -1018,22 +1018,22 @@
         </is>
       </c>
       <c r="E19">
-        <v>0.3264285154476826</v>
+        <v>0.2156401104627809</v>
       </c>
       <c r="F19">
-        <v>0.3504666632616568</v>
+        <v>0.3258793193248921</v>
       </c>
       <c r="G19">
-        <v>0.9314110289684603</v>
+        <v>0.6617176901851635</v>
       </c>
       <c r="H19">
-        <v>0.3516409879731301</v>
+        <v>0.5081521652543333</v>
       </c>
       <c r="I19">
-        <v>-0.3604735223270914</v>
+        <v>-0.4230716187204351</v>
       </c>
       <c r="J19">
-        <v>1.013330553222457</v>
+        <v>0.8543518396459968</v>
       </c>
     </row>
     <row r="20">
@@ -1053,22 +1053,22 @@
         </is>
       </c>
       <c r="E20">
-        <v>-0.06845583242240731</v>
+        <v>-0.2316351887021207</v>
       </c>
       <c r="F20">
-        <v>0.1049227543166014</v>
+        <v>0.1133897478036092</v>
       </c>
       <c r="G20">
-        <v>-0.6524402916058015</v>
+        <v>-2.042823034612549</v>
       </c>
       <c r="H20">
-        <v>0.5141171791873238</v>
+        <v>0.04106995945058138</v>
       </c>
       <c r="I20">
-        <v>-0.2741006520416905</v>
+        <v>-0.4538750106132745</v>
       </c>
       <c r="J20">
-        <v>0.1371889871968759</v>
+        <v>-0.009395366790966919</v>
       </c>
     </row>
     <row r="21">
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="E21">
-        <v>-0.2470673397072077</v>
+        <v>-0.4157762562757427</v>
       </c>
       <c r="F21">
-        <v>0.1387515298438262</v>
+        <v>0.1403442209229059</v>
       </c>
       <c r="G21">
-        <v>-1.780645878177328</v>
+        <v>-2.962546327462515</v>
       </c>
       <c r="H21">
-        <v>0.07497031989206154</v>
+        <v>0.003051058921454069</v>
       </c>
       <c r="I21">
-        <v>-0.5190153410009415</v>
+        <v>-0.6908458747229709</v>
       </c>
       <c r="J21">
-        <v>0.0248806615865261</v>
+        <v>-0.1407066378285145</v>
       </c>
     </row>
     <row r="22">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="E22">
-        <v>1.086706321957365</v>
+        <v>1.098454027269368</v>
       </c>
       <c r="F22">
-        <v>0.3411323100155927</v>
+        <v>0.2974514195505146</v>
       </c>
       <c r="G22">
-        <v>3.185586032316005</v>
+        <v>3.692885476657888</v>
       </c>
       <c r="H22">
-        <v>0.001444611443099513</v>
+        <v>0.0002217238891170347</v>
       </c>
       <c r="I22">
-        <v>0.4180992803638514</v>
+        <v>0.5154599578000458</v>
       </c>
       <c r="J22">
-        <v>1.755313363550879</v>
+        <v>1.68144809673869</v>
       </c>
     </row>
     <row r="23">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="E23">
-        <v>0.3275951907247254</v>
+        <v>0.2691177483618927</v>
       </c>
       <c r="F23">
-        <v>0.1595760780467131</v>
+        <v>0.1873138741256682</v>
       </c>
       <c r="G23">
-        <v>2.052909149884155</v>
+        <v>1.436720849526301</v>
       </c>
       <c r="H23">
-        <v>0.04008138945471573</v>
+        <v>0.1507973282520838</v>
       </c>
       <c r="I23">
-        <v>0.01483182495901492</v>
+        <v>-0.09801069872908608</v>
       </c>
       <c r="J23">
-        <v>0.6403585564904358</v>
+        <v>0.6362461954528715</v>
       </c>
     </row>
     <row r="24">
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="E24">
-        <v>0.1145227453523269</v>
+        <v>0.2056232840128128</v>
       </c>
       <c r="F24">
-        <v>0.2840838794463352</v>
+        <v>0.2068252919333884</v>
       </c>
       <c r="G24">
-        <v>0.4031300388305235</v>
+        <v>0.9941882933690587</v>
       </c>
       <c r="H24">
-        <v>0.6868525634576472</v>
+        <v>0.3201312063324294</v>
       </c>
       <c r="I24">
-        <v>-0.4422714269509086</v>
+        <v>-0.199746839268611</v>
       </c>
       <c r="J24">
-        <v>0.6713169176555623</v>
+        <v>0.6109934072942365</v>
       </c>
     </row>
     <row r="25">
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="E25">
-        <v>0.4344954143554534</v>
+        <v>0.3722791317156897</v>
       </c>
       <c r="F25">
-        <v>0.05306918765899882</v>
+        <v>0.04948509809880131</v>
       </c>
       <c r="G25">
-        <v>8.187338708618372</v>
+        <v>7.523055344305916</v>
       </c>
       <c r="H25">
-        <v>2.670657824954373E-16</v>
+        <v>5.351075852058362E-14</v>
       </c>
       <c r="I25">
-        <v>0.3304817178550182</v>
+        <v>0.2752901216706077</v>
       </c>
       <c r="J25">
-        <v>0.5385091108558885</v>
+        <v>0.4692681417607718</v>
       </c>
     </row>
     <row r="26">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E26">
-        <v>0.07643852084873663</v>
+        <v>0.09242578520457384</v>
       </c>
       <c r="F26">
-        <v>0.047371179240686</v>
+        <v>0.05460714123254123</v>
       </c>
       <c r="G26">
-        <v>1.613608148962553</v>
+        <v>1.692558576010859</v>
       </c>
       <c r="H26">
-        <v>0.1066124481658893</v>
+        <v>0.09053952156044508</v>
       </c>
       <c r="I26">
-        <v>-0.01640728436819937</v>
+        <v>-0.01460224490989913</v>
       </c>
       <c r="J26">
-        <v>0.1692843260656726</v>
+        <v>0.1994538153190468</v>
       </c>
     </row>
     <row r="27">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="E27">
-        <v>0.3765075582651198</v>
+        <v>0.3952034764890177</v>
       </c>
       <c r="F27">
-        <v>0.07875248472139278</v>
+        <v>0.09713501818614917</v>
       </c>
       <c r="G27">
-        <v>4.780897511959304</v>
+        <v>4.068599397713101</v>
       </c>
       <c r="H27">
-        <v>1.745143187650649E-06</v>
+        <v>4.729658407101319E-05</v>
       </c>
       <c r="I27">
-        <v>0.2221555245181492</v>
+        <v>0.2048223392065222</v>
       </c>
       <c r="J27">
-        <v>0.5308595920120905</v>
+        <v>0.5855846137715132</v>
       </c>
     </row>
     <row r="28">
@@ -1333,22 +1333,22 @@
         </is>
       </c>
       <c r="E28">
-        <v>-0.1150487718789137</v>
+        <v>0.207547377512728</v>
       </c>
       <c r="F28">
-        <v>0.274724159967129</v>
+        <v>0.3364674901724622</v>
       </c>
       <c r="G28">
-        <v>-0.4187792289279523</v>
+        <v>0.6168422910824044</v>
       </c>
       <c r="H28">
-        <v>0.6753774863475017</v>
+        <v>0.5373387541110926</v>
       </c>
       <c r="I28">
-        <v>-0.6534982310975069</v>
+        <v>-0.4519167851938823</v>
       </c>
       <c r="J28">
-        <v>0.4234006873396795</v>
+        <v>0.8670115402193384</v>
       </c>
     </row>
     <row r="29">
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E29">
-        <v>-0.08469758756259733</v>
+        <v>-0.1628475954510066</v>
       </c>
       <c r="F29">
-        <v>0.09637013352985258</v>
+        <v>0.1158275511373777</v>
       </c>
       <c r="G29">
-        <v>-0.8788779724618786</v>
+        <v>-1.405948704361889</v>
       </c>
       <c r="H29">
-        <v>0.3794674432781585</v>
+        <v>0.1597393572887263</v>
       </c>
       <c r="I29">
-        <v>-0.2735795784664242</v>
+        <v>-0.3898654240977381</v>
       </c>
       <c r="J29">
-        <v>0.1041844033412295</v>
+        <v>0.06417023319572493</v>
       </c>
     </row>
     <row r="30">
@@ -1403,22 +1403,22 @@
         </is>
       </c>
       <c r="E30">
-        <v>-0.174946477160223</v>
+        <v>-0.2703276284916296</v>
       </c>
       <c r="F30">
-        <v>0.1669346633805815</v>
+        <v>0.1434678692053761</v>
       </c>
       <c r="G30">
-        <v>-1.047993709738857</v>
+        <v>-1.884238122367678</v>
       </c>
       <c r="H30">
-        <v>0.2946415050025532</v>
+        <v>0.05953277306782511</v>
       </c>
       <c r="I30">
-        <v>-0.5021324051574801</v>
+        <v>-0.5515194850728697</v>
       </c>
       <c r="J30">
-        <v>0.1522394508370341</v>
+        <v>0.01086422808961068</v>
       </c>
     </row>
     <row r="31">
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="E31">
-        <v>1.017945560956468</v>
+        <v>0.7761902737175573</v>
       </c>
       <c r="F31">
-        <v>0.2841947671973334</v>
+        <v>0.3066801695744541</v>
       </c>
       <c r="G31">
-        <v>3.5818589166691</v>
+        <v>2.530943799837433</v>
       </c>
       <c r="H31">
-        <v>0.0003411580265680782</v>
+        <v>0.01137560737722823</v>
       </c>
       <c r="I31">
-        <v>0.4609340526549491</v>
+        <v>0.175108186578991</v>
       </c>
       <c r="J31">
-        <v>1.574957069257986</v>
+        <v>1.377272360856124</v>
       </c>
     </row>
     <row r="32">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="E32">
-        <v>0.5007500781814825</v>
+        <v>0.5374380851213022</v>
       </c>
       <c r="F32">
-        <v>0.202715363423204</v>
+        <v>0.1923199137673523</v>
       </c>
       <c r="G32">
-        <v>2.470212763973289</v>
+        <v>2.794500447683418</v>
       </c>
       <c r="H32">
-        <v>0.01350327124001773</v>
+        <v>0.005197996880709431</v>
       </c>
       <c r="I32">
-        <v>0.1034352667590546</v>
+        <v>0.1604979806274429</v>
       </c>
       <c r="J32">
-        <v>0.8980648896039105</v>
+        <v>0.9143781896151615</v>
       </c>
     </row>
     <row r="33">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="E33">
-        <v>-0.1067935774572977</v>
+        <v>-0.04212443170624765</v>
       </c>
       <c r="F33">
-        <v>0.1739682310301449</v>
+        <v>0.2037930553290638</v>
       </c>
       <c r="G33">
-        <v>-0.6138682725284061</v>
+        <v>-0.2067019979568465</v>
       </c>
       <c r="H33">
-        <v>0.5393023775183277</v>
+        <v>0.8362425969552246</v>
       </c>
       <c r="I33">
-        <v>-0.4477650447305252</v>
+        <v>-0.4415514804505911</v>
       </c>
       <c r="J33">
-        <v>0.2341778898159297</v>
+        <v>0.3573026170380958</v>
       </c>
     </row>
     <row r="34">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E34">
-        <v>0.03120163848253449</v>
+        <v>0.03750422641436646</v>
       </c>
       <c r="F34">
-        <v>0.07835460075252826</v>
+        <v>0.06644075755215176</v>
       </c>
       <c r="G34">
-        <v>0.3982106753511562</v>
+        <v>0.5644762009964747</v>
       </c>
       <c r="H34">
-        <v>0.6904748975008711</v>
+        <v>0.5724300923414392</v>
       </c>
       <c r="I34">
-        <v>-0.1223705570154359</v>
+        <v>-0.09271726549340856</v>
       </c>
       <c r="J34">
-        <v>0.1847738339805049</v>
+        <v>0.1677257183221415</v>
       </c>
     </row>
     <row r="35">
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="E35">
-        <v>0.2306615362505412</v>
+        <v>0.2200590004007081</v>
       </c>
       <c r="F35">
-        <v>0.07434662820356261</v>
+        <v>0.05042074264196222</v>
       </c>
       <c r="G35">
-        <v>3.10251509482024</v>
+        <v>4.364453771800772</v>
       </c>
       <c r="H35">
-        <v>0.001918837619383265</v>
+        <v>1.274407949096592E-05</v>
       </c>
       <c r="I35">
-        <v>0.08494482259956868</v>
+        <v>0.1212361607486992</v>
       </c>
       <c r="J35">
-        <v>0.3763782499015137</v>
+        <v>0.3188818400527169</v>
       </c>
     </row>
     <row r="36">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="E36">
-        <v>-0.1345914954830732</v>
+        <v>-0.09279477121186071</v>
       </c>
       <c r="F36">
-        <v>0.1624456789311983</v>
+        <v>0.138950281919934</v>
       </c>
       <c r="G36">
-        <v>-0.8285323215034706</v>
+        <v>-0.6678271532067201</v>
       </c>
       <c r="H36">
-        <v>0.407369098213704</v>
+        <v>0.504243931771504</v>
       </c>
       <c r="I36">
-        <v>-0.4529791756323789</v>
+        <v>-0.3651323194166182</v>
       </c>
       <c r="J36">
-        <v>0.1837961846662325</v>
+        <v>0.1795427769928968</v>
       </c>
     </row>
     <row r="37">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="E37">
-        <v>-0.222453909221228</v>
+        <v>-0.1794047704331339</v>
       </c>
       <c r="F37">
-        <v>0.2301052883046032</v>
+        <v>0.1854597226705753</v>
       </c>
       <c r="G37">
-        <v>-0.9667483561992428</v>
+        <v>-0.9673516591621532</v>
       </c>
       <c r="H37">
-        <v>0.3336698471327236</v>
+        <v>0.3333682671437722</v>
       </c>
       <c r="I37">
-        <v>-0.6734519869504558</v>
+        <v>-0.542899147450248</v>
       </c>
       <c r="J37">
-        <v>0.2285441685079999</v>
+        <v>0.1840896065839803</v>
       </c>
     </row>
     <row r="38">
@@ -1683,22 +1683,22 @@
         </is>
       </c>
       <c r="E38">
-        <v>-0.09935091222537569</v>
+        <v>-0.06939846094055388</v>
       </c>
       <c r="F38">
-        <v>0.05515982315425021</v>
+        <v>0.06009395973208371</v>
       </c>
       <c r="G38">
-        <v>-1.801146315272776</v>
+        <v>-1.154832553054456</v>
       </c>
       <c r="H38">
-        <v>0.07167982133097882</v>
+        <v>0.2481590036178647</v>
       </c>
       <c r="I38">
-        <v>-0.2074621790013046</v>
+        <v>-0.1871804577038382</v>
       </c>
       <c r="J38">
-        <v>0.008760354550553254</v>
+        <v>0.04838353582273043</v>
       </c>
     </row>
     <row r="39">
@@ -1718,22 +1718,22 @@
         </is>
       </c>
       <c r="E39">
-        <v>0.2389452207342184</v>
+        <v>0.3082608168555006</v>
       </c>
       <c r="F39">
-        <v>0.06357900101425773</v>
+        <v>0.07229832948062995</v>
       </c>
       <c r="G39">
-        <v>3.758241194771752</v>
+        <v>4.263733603113048</v>
       </c>
       <c r="H39">
-        <v>0.0001711118998335645</v>
+        <v>2.010391115479581E-05</v>
       </c>
       <c r="I39">
-        <v>0.1143326685732377</v>
+        <v>0.1665586949310555</v>
       </c>
       <c r="J39">
-        <v>0.3635577728951991</v>
+        <v>0.4499629387799457</v>
       </c>
     </row>
     <row r="40">
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="E40">
-        <v>-0.01496168163725679</v>
+        <v>-0.01061539947851988</v>
       </c>
       <c r="F40">
-        <v>0.01744008569183133</v>
+        <v>0.01777537768159808</v>
       </c>
       <c r="G40">
-        <v>-0.8578903740286443</v>
+        <v>-0.5971968454717815</v>
       </c>
       <c r="H40">
-        <v>0.3909530000175639</v>
+        <v>0.5503759650630907</v>
       </c>
       <c r="I40">
-        <v>-0.0491436214805385</v>
+        <v>-0.04545449954604919</v>
       </c>
       <c r="J40">
-        <v>0.01922025820602492</v>
+        <v>0.02422370058900943</v>
       </c>
     </row>
     <row r="41">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="E41">
-        <v>0.2163232876755045</v>
+        <v>0.2567592318315877</v>
       </c>
       <c r="F41">
-        <v>0.03737710980290163</v>
+        <v>0.04582282884590329</v>
       </c>
       <c r="G41">
-        <v>5.787587344667057</v>
+        <v>5.603303818169723</v>
       </c>
       <c r="H41">
-        <v>7.14045608402425E-09</v>
+        <v>2.103041211086462E-08</v>
       </c>
       <c r="I41">
-        <v>0.1430654986156183</v>
+        <v>0.1669481376238741</v>
       </c>
       <c r="J41">
-        <v>0.2895810767353907</v>
+        <v>0.3465703260393012</v>
       </c>
     </row>
     <row r="42">
@@ -1838,22 +1838,22 @@
         </is>
       </c>
       <c r="E42">
-        <v>-0.03192825785975611</v>
+        <v>-0.02711645882087103</v>
       </c>
       <c r="F42">
-        <v>0.01464145999735253</v>
+        <v>0.01621767052400044</v>
       </c>
       <c r="G42">
-        <v>-2.180674459072344</v>
+        <v>-1.672031675618366</v>
       </c>
       <c r="H42">
-        <v>0.02920750345984987</v>
+        <v>0.09451807609714412</v>
       </c>
       <c r="I42">
-        <v>-0.06062499213565099</v>
+        <v>-0.05890250896104871</v>
       </c>
       <c r="J42">
-        <v>-0.00323152358386123</v>
+        <v>0.004669591319306644</v>
       </c>
     </row>
     <row r="43">
@@ -1878,22 +1878,22 @@
         </is>
       </c>
       <c r="E43">
-        <v>0.2463352148862129</v>
+        <v>0.2700889788555508</v>
       </c>
       <c r="F43">
-        <v>0.03699732244508774</v>
+        <v>0.04446183875722785</v>
       </c>
       <c r="G43">
-        <v>6.65819033936386</v>
+        <v>6.074624586047834</v>
       </c>
       <c r="H43">
-        <v>2.772196218698916E-11</v>
+        <v>1.242781175636949E-09</v>
       </c>
       <c r="I43">
-        <v>0.1738217953694255</v>
+        <v>0.1829453762049571</v>
       </c>
       <c r="J43">
-        <v>0.3188486344030002</v>
+        <v>0.3572325815061445</v>
       </c>
     </row>
     <row r="44">
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="E44">
-        <v>-0.05403980305828984</v>
+        <v>-0.06306576334403555</v>
       </c>
       <c r="F44">
-        <v>0.01663784831167251</v>
+        <v>0.01852826587060957</v>
       </c>
       <c r="G44">
-        <v>-3.248004311974491</v>
+        <v>-3.403759627827529</v>
       </c>
       <c r="H44">
-        <v>0.00116217509408428</v>
+        <v>0.0006646521488910276</v>
       </c>
       <c r="I44">
-        <v>-0.08664938652940851</v>
+        <v>-0.09938049714641296</v>
       </c>
       <c r="J44">
-        <v>-0.02143021958717118</v>
+        <v>-0.02675102954165813</v>
       </c>
     </row>
     <row r="45">
@@ -1953,22 +1953,22 @@
         </is>
       </c>
       <c r="E45">
-        <v>3.177682238013741</v>
+        <v>3.283966335403539</v>
       </c>
       <c r="F45">
-        <v>0.1289143067901985</v>
+        <v>0.1328698010698853</v>
       </c>
       <c r="G45">
-        <v>24.64957006816363</v>
+        <v>24.71567134864812</v>
       </c>
       <c r="H45">
-        <v>3.719392239159806E-134</v>
+        <v>7.256685675019942E-135</v>
       </c>
       <c r="I45">
-        <v>2.925014839613005</v>
+        <v>3.023546310673562</v>
       </c>
       <c r="J45">
-        <v>3.430349636414477</v>
+        <v>3.544386360133516</v>
       </c>
     </row>
     <row r="46">
@@ -1988,22 +1988,22 @@
         </is>
       </c>
       <c r="E46">
-        <v>1.179418793136859</v>
+        <v>1.250904139162395</v>
       </c>
       <c r="F46">
-        <v>0.1429487684487492</v>
+        <v>0.147208738654022</v>
       </c>
       <c r="G46">
-        <v>8.250639763711648</v>
+        <v>8.497485615322999</v>
       </c>
       <c r="H46">
-        <v>1.575487997963018E-16</v>
+        <v>1.937415017098804E-17</v>
       </c>
       <c r="I46">
-        <v>0.8992443553429548</v>
+        <v>0.9623803131909423</v>
       </c>
       <c r="J46">
-        <v>1.459593230930763</v>
+        <v>1.539427965133847</v>
       </c>
     </row>
     <row r="47">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="E47">
-        <v>-1.558498258507122</v>
+        <v>-1.565765075090887</v>
       </c>
       <c r="F47">
-        <v>0.1370350358483479</v>
+        <v>0.1355251438866202</v>
       </c>
       <c r="G47">
-        <v>-11.37299121249444</v>
+        <v>-11.55331793191675</v>
       </c>
       <c r="H47">
-        <v>5.700012031177998E-30</v>
+        <v>7.102450286028647E-31</v>
       </c>
       <c r="I47">
-        <v>-1.82708199339004</v>
+        <v>-1.831389476108272</v>
       </c>
       <c r="J47">
-        <v>-1.289914523624205</v>
+        <v>-1.300140674073503</v>
       </c>
     </row>
     <row r="48">
@@ -2058,22 +2058,22 @@
         </is>
       </c>
       <c r="E48">
-        <v>-1.231169841753629</v>
+        <v>-1.248009073146</v>
       </c>
       <c r="F48">
-        <v>0.1734440048535871</v>
+        <v>0.1689747470020821</v>
       </c>
       <c r="G48">
-        <v>-7.098370697752983</v>
+        <v>-7.385772698512293</v>
       </c>
       <c r="H48">
-        <v>1.26236213936093E-12</v>
+        <v>1.515705394993914E-13</v>
       </c>
       <c r="I48">
-        <v>-1.57111384460105</v>
+        <v>-1.579193491566848</v>
       </c>
       <c r="J48">
-        <v>-0.8912258389062075</v>
+        <v>-0.9168246547251517</v>
       </c>
     </row>
     <row r="49">
@@ -2093,22 +2093,22 @@
         </is>
       </c>
       <c r="E49">
-        <v>-0.2251614844702914</v>
+        <v>-0.2129358283069731</v>
       </c>
       <c r="F49">
-        <v>0.1993082905080548</v>
+        <v>0.2114039351854462</v>
       </c>
       <c r="G49">
-        <v>-1.129714593890372</v>
+        <v>-1.007246284796842</v>
       </c>
       <c r="H49">
-        <v>0.2585965057606038</v>
+        <v>0.3138164357416326</v>
       </c>
       <c r="I49">
-        <v>-0.615798555686325</v>
+        <v>-0.6272799274604874</v>
       </c>
       <c r="J49">
-        <v>0.1654755867457422</v>
+        <v>0.2014082708465412</v>
       </c>
     </row>
     <row r="50">
@@ -2128,22 +2128,22 @@
         </is>
       </c>
       <c r="E50">
-        <v>0.6867994862764141</v>
+        <v>0.7035384189204821</v>
       </c>
       <c r="F50">
-        <v>0.02111053228511903</v>
+        <v>0.02175306323376813</v>
       </c>
       <c r="G50">
-        <v>32.53349925053969</v>
+        <v>32.34203897446278</v>
       </c>
       <c r="H50">
-        <v>3.583896438877288E-232</v>
+        <v>1.795225764344333E-229</v>
       </c>
       <c r="I50">
-        <v>0.6454236033031108</v>
+        <v>0.6609031984288741</v>
       </c>
       <c r="J50">
-        <v>0.7281753692497174</v>
+        <v>0.74617363941209</v>
       </c>
     </row>
     <row r="51">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="E51">
-        <v>0.4079685803229046</v>
+        <v>0.4199303076485714</v>
       </c>
       <c r="F51">
-        <v>0.05003866810397157</v>
+        <v>0.05275120934911571</v>
       </c>
       <c r="G51">
-        <v>8.15306633412419</v>
+        <v>7.960581621350277</v>
       </c>
       <c r="H51">
-        <v>3.548108627782903E-16</v>
+        <v>1.712324557017409E-15</v>
       </c>
       <c r="I51">
-        <v>0.3098945930047672</v>
+        <v>0.3165398371833721</v>
       </c>
       <c r="J51">
-        <v>0.5060425676410419</v>
+        <v>0.5233207781137708</v>
       </c>
     </row>
     <row r="52">
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="E52">
-        <v>0.03053388366179355</v>
+        <v>0.02970847412932393</v>
       </c>
       <c r="F52">
-        <v>0.02500130610395286</v>
+        <v>0.02534988758364396</v>
       </c>
       <c r="G52">
-        <v>1.221291541123364</v>
+        <v>1.171937115354002</v>
       </c>
       <c r="H52">
-        <v>0.221975654993345</v>
+        <v>0.2412223043687733</v>
       </c>
       <c r="I52">
-        <v>-0.01846777586841547</v>
+        <v>-0.01997639254675732</v>
       </c>
       <c r="J52">
-        <v>0.07953554319200257</v>
+        <v>0.07939334080540517</v>
       </c>
     </row>
     <row r="53">
@@ -2233,22 +2233,22 @@
         </is>
       </c>
       <c r="E53">
-        <v>-0.05559356817658333</v>
+        <v>-0.05040829789342704</v>
       </c>
       <c r="F53">
-        <v>0.02743278500265633</v>
+        <v>0.02795533989347903</v>
       </c>
       <c r="G53">
-        <v>-2.026537523302872</v>
+        <v>-1.803172420206755</v>
       </c>
       <c r="H53">
-        <v>0.04270973153966753</v>
+        <v>0.07136114042239228</v>
       </c>
       <c r="I53">
-        <v>-0.1093608387774203</v>
+        <v>-0.1051997572602217</v>
       </c>
       <c r="J53">
-        <v>-0.001826297575746413</v>
+        <v>0.00438316147336764</v>
       </c>
     </row>
     <row r="54">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="E54">
-        <v>0.1869933616082073</v>
+        <v>0.2154207880174238</v>
       </c>
       <c r="F54">
-        <v>0.03663080761380769</v>
+        <v>0.03930206356256948</v>
       </c>
       <c r="G54">
-        <v>5.104811326565502</v>
+        <v>5.481157183374624</v>
       </c>
       <c r="H54">
-        <v>3.311247177346199E-07</v>
+        <v>4.225528519619444E-08</v>
       </c>
       <c r="I54">
-        <v>0.1151982979605287</v>
+        <v>0.1383901589166836</v>
       </c>
       <c r="J54">
-        <v>0.258788425255886</v>
+        <v>0.2924514171181639</v>
       </c>
     </row>
     <row r="55">
@@ -2303,22 +2303,22 @@
         </is>
       </c>
       <c r="E55">
-        <v>0.07788785415915504</v>
+        <v>0.1356866845789972</v>
       </c>
       <c r="F55">
-        <v>0.03213479313437909</v>
+        <v>0.03729859110363051</v>
       </c>
       <c r="G55">
-        <v>2.423785764963506</v>
+        <v>3.637850132247754</v>
       </c>
       <c r="H55">
-        <v>0.01535966353794925</v>
+        <v>0.000274923312298882</v>
       </c>
       <c r="I55">
-        <v>0.01490481696512704</v>
+        <v>0.0625827893417953</v>
       </c>
       <c r="J55">
-        <v>0.140870891353183</v>
+        <v>0.208790579816199</v>
       </c>
     </row>
     <row r="56">
@@ -2338,22 +2338,22 @@
         </is>
       </c>
       <c r="E56">
-        <v>-0.01433275009832291</v>
+        <v>-0.00555897596176698</v>
       </c>
       <c r="F56">
-        <v>0.03402625276654869</v>
+        <v>0.02976363114335306</v>
       </c>
       <c r="G56">
-        <v>-0.4212262277794364</v>
+        <v>-0.1867707584129376</v>
       </c>
       <c r="H56">
-        <v>0.6735898940824505</v>
+        <v>0.8518403748547207</v>
       </c>
       <c r="I56">
-        <v>-0.0810229800496147</v>
+        <v>-0.06389462105187368</v>
       </c>
       <c r="J56">
-        <v>0.05235747985296887</v>
+        <v>0.05277666912833973</v>
       </c>
     </row>
     <row r="57">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="E57">
-        <v>0.03589956979820254</v>
+        <v>0.03236488463072135</v>
       </c>
       <c r="F57">
-        <v>0.0163359496467969</v>
+        <v>0.01048406733333515</v>
       </c>
       <c r="G57">
-        <v>2.197580830891066</v>
+        <v>3.087054251150594</v>
       </c>
       <c r="H57">
-        <v>0.02797899049230319</v>
+        <v>0.002021506995377402</v>
       </c>
       <c r="I57">
-        <v>0.003881696837220817</v>
+        <v>0.01181649024589157</v>
       </c>
       <c r="J57">
-        <v>0.06791744275918427</v>
+        <v>0.05291327901555112</v>
       </c>
     </row>
     <row r="58">
@@ -2408,22 +2408,22 @@
         </is>
       </c>
       <c r="E58">
-        <v>0.05701962521739354</v>
+        <v>0.05046108289828877</v>
       </c>
       <c r="F58">
-        <v>0.009127570403648899</v>
+        <v>0.008251336613744685</v>
       </c>
       <c r="G58">
-        <v>6.246966355318277</v>
+        <v>6.11550410078206</v>
       </c>
       <c r="H58">
-        <v>4.185011615814005E-10</v>
+        <v>9.62522073807318E-10</v>
       </c>
       <c r="I58">
-        <v>0.03912991595988798</v>
+        <v>0.03428876031103251</v>
       </c>
       <c r="J58">
-        <v>0.0749093344748991</v>
+        <v>0.06663340548554504</v>
       </c>
     </row>
     <row r="59">
@@ -2443,22 +2443,22 @@
         </is>
       </c>
       <c r="E59">
-        <v>-1.59986104271923E-05</v>
+        <v>0.02366858935564152</v>
       </c>
       <c r="F59">
-        <v>0.01843319411678112</v>
+        <v>0.02215454807126237</v>
       </c>
       <c r="G59">
-        <v>-0.0008679239379694677</v>
+        <v>1.068339976040544</v>
       </c>
       <c r="H59">
-        <v>0.9993074969768858</v>
+        <v>0.285367182137671</v>
       </c>
       <c r="I59">
-        <v>-0.03614439519935379</v>
+        <v>-0.01975352695779403</v>
       </c>
       <c r="J59">
-        <v>0.03611239797849941</v>
+        <v>0.06709070566907707</v>
       </c>
     </row>
     <row r="60">
@@ -2478,22 +2478,22 @@
         </is>
       </c>
       <c r="E60">
-        <v>0.009994197514885851</v>
+        <v>0.02766343036097121</v>
       </c>
       <c r="F60">
-        <v>0.01835056735367237</v>
+        <v>0.02093028160213836</v>
       </c>
       <c r="G60">
-        <v>0.5446260773450027</v>
+        <v>1.321694131346276</v>
       </c>
       <c r="H60">
-        <v>0.5860107158108434</v>
+        <v>0.1862700236774889</v>
       </c>
       <c r="I60">
-        <v>-0.02597225359418848</v>
+        <v>-0.01335916776550127</v>
       </c>
       <c r="J60">
-        <v>0.04596064862396019</v>
+        <v>0.06868602848744368</v>
       </c>
     </row>
     <row r="61">
@@ -2513,22 +2513,22 @@
         </is>
       </c>
       <c r="E61">
-        <v>0.004363143115477153</v>
+        <v>0.006045896096404967</v>
       </c>
       <c r="F61">
-        <v>0.006931667524176943</v>
+        <v>0.007396836170168555</v>
       </c>
       <c r="G61">
-        <v>0.629450720228424</v>
+        <v>0.8173624448771855</v>
       </c>
       <c r="H61">
-        <v>0.5290540214544296</v>
+        <v>0.4137213308008554</v>
       </c>
       <c r="I61">
-        <v>-0.009222675584715578</v>
+        <v>-0.008451636396668585</v>
       </c>
       <c r="J61">
-        <v>0.01794896181566988</v>
+        <v>0.02054342858947852</v>
       </c>
     </row>
     <row r="62">
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="E62">
-        <v>-0.002771863384026128</v>
+        <v>-0.004725744922190714</v>
       </c>
       <c r="F62">
-        <v>0.00283379109537566</v>
+        <v>0.003121356488942858</v>
       </c>
       <c r="G62">
-        <v>-0.9781466913878766</v>
+        <v>-1.514003587520768</v>
       </c>
       <c r="H62">
-        <v>0.3280017777180042</v>
+        <v>0.1300249295994683</v>
       </c>
       <c r="I62">
-        <v>-0.00832599187067273</v>
+        <v>-0.01084349122342911</v>
       </c>
       <c r="J62">
-        <v>0.002782265102620473</v>
+        <v>0.001392001379047681</v>
       </c>
     </row>
     <row r="63">
@@ -2583,22 +2583,22 @@
         </is>
       </c>
       <c r="E63">
-        <v>-0.002877860066302895</v>
+        <v>0.004336424077710542</v>
       </c>
       <c r="F63">
-        <v>0.009321914772890618</v>
+        <v>0.007550384403668423</v>
       </c>
       <c r="G63">
-        <v>-0.3087198431240863</v>
+        <v>0.5743315632517533</v>
       </c>
       <c r="H63">
-        <v>0.7575346480462455</v>
+        <v>0.56574345424968</v>
       </c>
       <c r="I63">
-        <v>-0.02114847728812038</v>
+        <v>-0.0104620574229125</v>
       </c>
       <c r="J63">
-        <v>0.01539275715551459</v>
+        <v>0.01913490557833358</v>
       </c>
     </row>
     <row r="64">
@@ -2618,22 +2618,22 @@
         </is>
       </c>
       <c r="E64">
-        <v>0.2735318330205881</v>
+        <v>0.3205071813780392</v>
       </c>
       <c r="F64">
-        <v>0.05541334801948872</v>
+        <v>0.05407634171785997</v>
       </c>
       <c r="G64">
-        <v>4.936208382940294</v>
+        <v>5.926939049432485</v>
       </c>
       <c r="H64">
-        <v>7.965599649932856E-07</v>
+        <v>3.086334641629018E-09</v>
       </c>
       <c r="I64">
-        <v>0.1649236666396063</v>
+        <v>0.2145194991953528</v>
       </c>
       <c r="J64">
-        <v>0.38213999940157</v>
+        <v>0.4264948635607255</v>
       </c>
     </row>
     <row r="65">
@@ -2653,22 +2653,22 @@
         </is>
       </c>
       <c r="E65">
-        <v>0.05390042370144658</v>
+        <v>0.04982934248328001</v>
       </c>
       <c r="F65">
-        <v>0.05651029666192425</v>
+        <v>0.05780692263796849</v>
       </c>
       <c r="G65">
-        <v>0.9538159748816861</v>
+        <v>0.8619961106622084</v>
       </c>
       <c r="H65">
-        <v>0.3401768016574903</v>
+        <v>0.388689658092269</v>
       </c>
       <c r="I65">
-        <v>-0.05685772251159898</v>
+        <v>-0.06347014394423134</v>
       </c>
       <c r="J65">
-        <v>0.1646585699144921</v>
+        <v>0.1631288289107914</v>
       </c>
     </row>
   </sheetData>
